--- a/public/outils/matrices/capacite-emprunt-et-bilan-patrimonial.xlsx
+++ b/public/outils/matrices/capacite-emprunt-et-bilan-patrimonial.xlsx
@@ -34,7 +34,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="539">
   <si>
-    <t>CorpusImmo  ·  corpus.immo  ·  Estimer, comparer, décider. Sur les ventes réelles.</t>
+    <t>CorpusImmo  ·  www.corpus.immo  ·  Estimer, comparer, décider. Sur les ventes réelles.</t>
   </si>
   <si>
     <t>Mode d'emploi</t>
@@ -52,7 +52,7 @@
     <t>Le second onglet dresse le bilan patrimonial du foyer, ce que la banque regarde après les revenus : ce qu'il possède, ce qu'il doit, ce qu'il peut mobiliser comme apport, et ce que deviendra son patrimoine le jour de l'achat.</t>
   </si>
   <si>
-    <t>Deux onglets de saisie pour le dossier, remplis de haut en bas : les cellules bleues se remplissent, tout le reste se calcule. Un troisième onglet, Paramètres, ne se touche qu'à la mise à jour des barèmes.</t>
+    <t>Deux onglets de saisie pour le dossier, remplis de haut en bas : les cellules violettes se remplissent, tout le reste se calcule. Un troisième onglet, Paramètres, ne se touche qu'à la mise à jour des barèmes.</t>
   </si>
   <si>
     <t>Vous êtes</t>
@@ -163,7 +163,7 @@
     <t>Ce que vous faites</t>
   </si>
   <si>
-    <t>Fond bleu clair</t>
+    <t>Fond violet clair</t>
   </si>
   <si>
     <t>Saisie utilisateur</t>
@@ -190,7 +190,7 @@
     <t>Vous la lisez. C'est un chiffre à retenir. Le gras est le repère, pas la couleur.</t>
   </si>
   <si>
-    <t>Bandeau bleu nuit</t>
+    <t>Bandeau violet</t>
   </si>
   <si>
     <t>Titre de section</t>
@@ -235,10 +235,10 @@
     <t>0. L'exemple livré</t>
   </si>
   <si>
-    <t>Toutes les cellules bleues des onglets Capacité d'emprunt et Bilan patrimonial</t>
-  </si>
-  <si>
-    <t>Le classeur est livré rempli d'un exemple (section « Exemple guidé »). Gardez-le pour vous repérer, ou remplacez chaque cellule bleue par votre valeur. Mettez 0 dans celles qui ne vous concernent pas, ne laissez jamais une cellule bleue vide et gardez un choix dans chaque liste : le contrôle C70 passe au rouge sinon. Vérifiez surtout les saisies secondaires qui n'ont pas de raison d'être chez vous : loyers encaissés (C10), crédits en cours (C15, C16), loyer payé (C18), loyer du bien financé (C27), les trois choix Oui / Non (C32 à C34), et dans le Bilan patrimonial le bien locatif (C8), son encours (C24), le restant dû du crédit auto (C25) et les quatre postes d'épargne (C13 à C16).</t>
+    <t>Toutes les cellules violettes des onglets Capacité d'emprunt et Bilan patrimonial</t>
+  </si>
+  <si>
+    <t>Le classeur est livré rempli d'un exemple (section « Exemple guidé »). Gardez-le pour vous repérer, ou remplacez chaque cellule violette par votre valeur. Mettez 0 dans celles qui ne vous concernent pas, ne laissez jamais une cellule violette vide et gardez un choix dans chaque liste : le contrôle C70 passe au rouge sinon. Vérifiez surtout les saisies secondaires qui n'ont pas de raison d'être chez vous : loyers encaissés (C10), crédits en cours (C15, C16), loyer payé (C18), loyer du bien financé (C27), les trois choix Oui / Non (C32 à C34), et dans le Bilan patrimonial le bien locatif (C8), son encours (C24), le restant dû du crédit auto (C25) et les quatre postes d'épargne (C13 à C16).</t>
   </si>
   <si>
     <t>Une saisie résiduelle de l'exemple est l'erreur la plus probable d'un premier usage : les 700 € de loyers ou les 450 € de crédit de l'exemple 2026, s'ils ne sont pas les vôtres, déplacent le prix maximal de plusieurs dizaines de milliers d'euros.</t>
@@ -442,7 +442,7 @@
     <t xml:space="preserve">  LES DONNÉES À METTRE À JOUR, OÙ ET POURQUOI</t>
   </si>
   <si>
-    <t>Deux familles de données. Les benchmarks (règles HCSF, droits de mutation, émoluments, taux de crédit de référence, pondérations et minimums bancaires) changent avec la loi ou le marché, à date fixe, et se rafraîchissent depuis une source indiquée. Les données de projet (revenus, charges, apport, taux, durée, patrimoine) sont propres à chaque dossier. L'architecture du classeur ne change pas quand les données changent : seules les cellules bleues bougent.</t>
+    <t>Deux familles de données. Les benchmarks (règles HCSF, droits de mutation, émoluments, taux de crédit de référence, pondérations et minimums bancaires) changent avec la loi ou le marché, à date fixe, et se rafraîchissent depuis une source indiquée. Les données de projet (revenus, charges, apport, taux, durée, patrimoine) sont propres à chaque dossier. L'architecture du classeur ne change pas quand les données changent : seules les cellules violettes bougent.</t>
   </si>
   <si>
     <t>Paramètre</t>
@@ -580,7 +580,7 @@
     <t>Revenus, charges, foyer, projet, patrimoine</t>
   </si>
   <si>
-    <t>Capacité d'emprunt!C7:C11, Capacité d'emprunt!C15:C18, Capacité d'emprunt!C22:C23, Capacité d'emprunt!C26:C34, toutes les cellules bleues du Bilan patrimonial</t>
+    <t>Capacité d'emprunt!C7:C11, Capacité d'emprunt!C15:C18, Capacité d'emprunt!C22:C23, Capacité d'emprunt!C26:C34, toutes les cellules violettes du Bilan patrimonial</t>
   </si>
   <si>
     <t>Tout le reste</t>
@@ -679,7 +679,7 @@
     <t>Jusqu'où la banque peut vous suivre, et ce qu'il vous reste pour vivre.</t>
   </si>
   <si>
-    <t>Cellules bleues : à remplir.  Cellules blanches : calculées automatiquement.</t>
+    <t>Cellules violettes : à remplir.  Cellules blanches : calculées automatiquement.</t>
   </si>
   <si>
     <t xml:space="preserve">  REVENUS MENSUELS NETS DU FOYER</t>
@@ -1174,7 +1174,7 @@
     <t>Saisies du bilan complètes et positives</t>
   </si>
   <si>
-    <t>À CORRIGER : unecellule bleue de cet onglet est vide, n'est pas un nombre ou est négative.</t>
+    <t>À CORRIGER : unecellule violette de cet onglet est vide, n'est pas un nombre ou est négative.</t>
   </si>
   <si>
     <t xml:space="preserve">  PRO FORMA APRÈS L'OPÉRATION (AU PRIX MAXIMAL)</t>
@@ -1680,7 +1680,7 @@
     <font>
       <b/>
       <sz val="16"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1700,19 +1700,19 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1724,7 +1724,7 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -1737,12 +1737,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0E1A33"/>
+        <fgColor rgb="FF4B3D7C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8F0FE"/>
+        <fgColor rgb="FFF1EEF8"/>
       </patternFill>
     </fill>
     <fill>
@@ -1752,7 +1752,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5F9FF"/>
+        <fgColor rgb="FFF8F6FC"/>
       </patternFill>
     </fill>
   </fills>
@@ -2124,6 +2124,171 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="10458450" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10458450" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="9963150" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9963150" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="9963150" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9963150" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="13258800" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13258800" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="8382000" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8382000" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3429,13 +3594,14 @@
     <mergeCell ref="D35:E35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
-    <tabColor rgb="FF3B6EF6"/>
+    <tabColor rgb="FF6C5AB0"/>
   </sheetPr>
   <dimension ref="B1:D72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4222,6 +4388,7 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="7">
@@ -4291,7 +4458,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
-    <tabColor rgb="FF0B8578"/>
+    <tabColor rgb="FF8B7CC4"/>
   </sheetPr>
   <dimension ref="B1:D58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4857,13 +5024,14 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
-    <tabColor rgb="FFB08C4E"/>
+    <tabColor rgb="FF495669"/>
   </sheetPr>
   <dimension ref="B1:F61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -5667,13 +5835,14 @@
     <mergeCell ref="B61:F61"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
-    <tabColor rgb="FF5A6B8C"/>
+    <tabColor rgb="FF8A93A6"/>
   </sheetPr>
   <dimension ref="B1:C62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -6159,5 +6328,6 @@
     <mergeCell ref="B27:C27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>